--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/197.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/197.xlsx
@@ -426,13 +426,13 @@
         <v>-15.27326579997617</v>
       </c>
       <c r="E2">
-        <v>-12.91116601929461</v>
+        <v>-18.35703187686085</v>
       </c>
       <c r="F2">
-        <v>8.700513026475571</v>
+        <v>10.05029765967504</v>
       </c>
       <c r="G2">
-        <v>-14.82954685674161</v>
+        <v>-18.05121252464721</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.85018244415816</v>
       </c>
       <c r="E3">
-        <v>-12.26869329793039</v>
+        <v>-17.99522944601803</v>
       </c>
       <c r="F3">
-        <v>8.72379350343253</v>
+        <v>10.56051861074625</v>
       </c>
       <c r="G3">
-        <v>-13.68214156774007</v>
+        <v>-17.43505875469636</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.3558530242592</v>
       </c>
       <c r="E4">
-        <v>-11.88484625561822</v>
+        <v>-18.41796702310807</v>
       </c>
       <c r="F4">
-        <v>8.692993590789063</v>
+        <v>10.03498797459048</v>
       </c>
       <c r="G4">
-        <v>-14.23549759935647</v>
+        <v>-16.84300906681695</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.82462215424778</v>
       </c>
       <c r="E5">
-        <v>-12.10600786920483</v>
+        <v>-17.00269662691287</v>
       </c>
       <c r="F5">
-        <v>8.93785669719882</v>
+        <v>9.704916738812338</v>
       </c>
       <c r="G5">
-        <v>-11.4630332345835</v>
+        <v>-15.80813418651355</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.25610891756971</v>
       </c>
       <c r="E6">
-        <v>-12.76035877789117</v>
+        <v>-20.01724290365693</v>
       </c>
       <c r="F6">
-        <v>9.019783387910417</v>
+        <v>9.651385895164569</v>
       </c>
       <c r="G6">
-        <v>-11.20191726571902</v>
+        <v>-15.35389423307015</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.66063696959044</v>
       </c>
       <c r="E7">
-        <v>-13.2271946348679</v>
+        <v>-18.60749271727709</v>
       </c>
       <c r="F7">
-        <v>9.101052840667107</v>
+        <v>9.583652376867139</v>
       </c>
       <c r="G7">
-        <v>-10.89161983232314</v>
+        <v>-14.43072378035284</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.04062042313323</v>
       </c>
       <c r="E8">
-        <v>-14.96813476779872</v>
+        <v>-20.09647308489513</v>
       </c>
       <c r="F8">
-        <v>8.534819378778634</v>
+        <v>10.34431107917045</v>
       </c>
       <c r="G8">
-        <v>-8.83308951054892</v>
+        <v>-13.47461671006531</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.42122878984596</v>
       </c>
       <c r="E9">
-        <v>-13.83828955983298</v>
+        <v>-21.24237173321806</v>
       </c>
       <c r="F9">
-        <v>8.642033101842053</v>
+        <v>9.941318104515899</v>
       </c>
       <c r="G9">
-        <v>-6.735272944860172</v>
+        <v>-10.81304403394853</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.81733997206853</v>
       </c>
       <c r="E10">
-        <v>-15.39607556152357</v>
+        <v>-20.17891395420477</v>
       </c>
       <c r="F10">
-        <v>8.749528724558422</v>
+        <v>10.04082234718296</v>
       </c>
       <c r="G10">
-        <v>-6.937838605317097</v>
+        <v>-11.41686105594728</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.24356070982977</v>
       </c>
       <c r="E11">
-        <v>-15.43952626962716</v>
+        <v>-23.86527746388276</v>
       </c>
       <c r="F11">
-        <v>8.871752812288376</v>
+        <v>10.40483081702306</v>
       </c>
       <c r="G11">
-        <v>-6.100383142429822</v>
+        <v>-10.9349383207045</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.708345762782939</v>
       </c>
       <c r="E12">
-        <v>-15.95275634281248</v>
+        <v>-21.14227887222652</v>
       </c>
       <c r="F12">
-        <v>9.375813147348529</v>
+        <v>10.11227757438167</v>
       </c>
       <c r="G12">
-        <v>-7.297972991261173</v>
+        <v>-9.811885404689839</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.218411922795784</v>
       </c>
       <c r="E13">
-        <v>-16.89692958798972</v>
+        <v>-21.74615088114937</v>
       </c>
       <c r="F13">
-        <v>8.934244264005702</v>
+        <v>10.37031236289014</v>
       </c>
       <c r="G13">
-        <v>-5.140199135310685</v>
+        <v>-9.464188738336803</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.795261897827327</v>
       </c>
       <c r="E14">
-        <v>-18.04324485592136</v>
+        <v>-22.48688243153202</v>
       </c>
       <c r="F14">
-        <v>9.322188865051748</v>
+        <v>10.32020390772563</v>
       </c>
       <c r="G14">
-        <v>-5.692874849818774</v>
+        <v>-8.218370862089349</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.44527770832828</v>
       </c>
       <c r="E15">
-        <v>-18.90560216120203</v>
+        <v>-23.16827738699217</v>
       </c>
       <c r="F15">
-        <v>9.454292110282214</v>
+        <v>10.12872436031351</v>
       </c>
       <c r="G15">
-        <v>-2.847997267192551</v>
+        <v>-7.69799282986239</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.170817714012491</v>
       </c>
       <c r="E16">
-        <v>-20.40307794605846</v>
+        <v>-24.89716272211457</v>
       </c>
       <c r="F16">
-        <v>10.12301034937061</v>
+        <v>10.09917399163733</v>
       </c>
       <c r="G16">
-        <v>-3.778383053912707</v>
+        <v>-7.184725849453785</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.963595348315554</v>
       </c>
       <c r="E17">
-        <v>-20.92160633383275</v>
+        <v>-26.8023596642516</v>
       </c>
       <c r="F17">
-        <v>9.668385394460897</v>
+        <v>11.05231789460906</v>
       </c>
       <c r="G17">
-        <v>-3.646209523257305</v>
+        <v>-8.53287599886565</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.82122684472019</v>
       </c>
       <c r="E18">
-        <v>-20.6935704967025</v>
+        <v>-25.5716970394531</v>
       </c>
       <c r="F18">
-        <v>10.3482244164875</v>
+        <v>10.27328345256891</v>
       </c>
       <c r="G18">
-        <v>-3.265801356430732</v>
+        <v>-7.067903318463983</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.745360043003228</v>
       </c>
       <c r="E19">
-        <v>-22.55469180132287</v>
+        <v>-27.60169419676752</v>
       </c>
       <c r="F19">
-        <v>10.57538802558631</v>
+        <v>10.64049734318185</v>
       </c>
       <c r="G19">
-        <v>-4.152497873669127</v>
+        <v>-7.031758782266221</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.729335480786128</v>
       </c>
       <c r="E20">
-        <v>-23.88860363349626</v>
+        <v>-27.78478945784565</v>
       </c>
       <c r="F20">
-        <v>10.34997124411223</v>
+        <v>11.44430886426906</v>
       </c>
       <c r="G20">
-        <v>-4.04124036973084</v>
+        <v>-7.820423424995717</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.764623939234416</v>
       </c>
       <c r="E21">
-        <v>-23.07633125074043</v>
+        <v>-30.27716871795025</v>
       </c>
       <c r="F21">
-        <v>11.065953602541</v>
+        <v>11.20698103060497</v>
       </c>
       <c r="G21">
-        <v>-3.869515751517765</v>
+        <v>-6.645024162914099</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.836526329431358</v>
       </c>
       <c r="E22">
-        <v>-25.82819433572156</v>
+        <v>-30.20782872394481</v>
       </c>
       <c r="F22">
-        <v>11.19710979163403</v>
+        <v>11.11578807658213</v>
       </c>
       <c r="G22">
-        <v>-3.472594583541306</v>
+        <v>-4.250638996180821</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.941926312130154</v>
       </c>
       <c r="E23">
-        <v>-24.16295217430296</v>
+        <v>-28.94588566493832</v>
       </c>
       <c r="F23">
-        <v>10.81454028846499</v>
+        <v>11.24282821400094</v>
       </c>
       <c r="G23">
-        <v>-2.589562840214885</v>
+        <v>-5.943747990784745</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.077266798467178</v>
       </c>
       <c r="E24">
-        <v>-23.73126180409976</v>
+        <v>-29.95693088578684</v>
       </c>
       <c r="F24">
-        <v>11.17957816715012</v>
+        <v>11.45619299345852</v>
       </c>
       <c r="G24">
-        <v>-3.101979010419897</v>
+        <v>-6.335938389185585</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.23421800665071</v>
       </c>
       <c r="E25">
-        <v>-25.06574422399811</v>
+        <v>-29.65594133239302</v>
       </c>
       <c r="F25">
-        <v>10.68012483259798</v>
+        <v>11.57422817904214</v>
       </c>
       <c r="G25">
-        <v>-1.866298024613691</v>
+        <v>-5.451443384730805</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.402300584207502</v>
       </c>
       <c r="E26">
-        <v>-25.16557443349721</v>
+        <v>-31.13908676125218</v>
       </c>
       <c r="F26">
-        <v>10.66959952308397</v>
+        <v>11.93691267073692</v>
       </c>
       <c r="G26">
-        <v>-2.82279077345654</v>
+        <v>-5.285406283754198</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.567324415670965</v>
       </c>
       <c r="E27">
-        <v>-25.45823159471691</v>
+        <v>-30.44231763653599</v>
       </c>
       <c r="F27">
-        <v>11.03315822044408</v>
+        <v>11.42704646979077</v>
       </c>
       <c r="G27">
-        <v>-2.868542512809268</v>
+        <v>-5.738755700447533</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.726597155945957</v>
       </c>
       <c r="E28">
-        <v>-25.46906823301726</v>
+        <v>-30.99063659056973</v>
       </c>
       <c r="F28">
-        <v>11.01970147128059</v>
+        <v>11.48221011423736</v>
       </c>
       <c r="G28">
-        <v>-2.975615487185916</v>
+        <v>-5.881645467013557</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.875128940291356</v>
       </c>
       <c r="E29">
-        <v>-25.84273073728618</v>
+        <v>-30.44082097587645</v>
       </c>
       <c r="F29">
-        <v>10.94383087198963</v>
+        <v>11.34179558036266</v>
       </c>
       <c r="G29">
-        <v>-2.946197979523952</v>
+        <v>-5.136683335947979</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.006119858907613</v>
       </c>
       <c r="E30">
-        <v>-25.29070069880315</v>
+        <v>-29.96774714595416</v>
       </c>
       <c r="F30">
-        <v>10.46635937554379</v>
+        <v>11.25519062237686</v>
       </c>
       <c r="G30">
-        <v>-2.970818506699512</v>
+        <v>-4.451304403498204</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.110671735414019</v>
       </c>
       <c r="E31">
-        <v>-26.63183997549277</v>
+        <v>-32.24147809554641</v>
       </c>
       <c r="F31">
-        <v>10.63545165613526</v>
+        <v>11.05414232382365</v>
       </c>
       <c r="G31">
-        <v>-3.774307772353864</v>
+        <v>-5.356864409219367</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.179928118849555</v>
       </c>
       <c r="E32">
-        <v>-26.32264482719706</v>
+        <v>-30.68710429902061</v>
       </c>
       <c r="F32">
-        <v>10.68834426629911</v>
+        <v>11.05722104812327</v>
       </c>
       <c r="G32">
-        <v>-3.228633861661334</v>
+        <v>-5.023806975240989</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.216886107657258</v>
       </c>
       <c r="E33">
-        <v>-25.06782732204164</v>
+        <v>-30.4837735518392</v>
       </c>
       <c r="F33">
-        <v>10.87688128812034</v>
+        <v>10.83754995171041</v>
       </c>
       <c r="G33">
-        <v>-2.754090332425584</v>
+        <v>-5.050619083563546</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.220622871341869</v>
       </c>
       <c r="E34">
-        <v>-24.95978698916664</v>
+        <v>-29.05252669934495</v>
       </c>
       <c r="F34">
-        <v>11.28782288276449</v>
+        <v>11.46081424731977</v>
       </c>
       <c r="G34">
-        <v>-1.990890405984162</v>
+        <v>-6.062520433097177</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.190193364969209</v>
       </c>
       <c r="E35">
-        <v>-24.73189153473063</v>
+        <v>-31.17341032999331</v>
       </c>
       <c r="F35">
-        <v>10.78194128590158</v>
+        <v>10.8409549194286</v>
       </c>
       <c r="G35">
-        <v>-2.906531022872405</v>
+        <v>-6.42299249468626</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.121539579162533</v>
       </c>
       <c r="E36">
-        <v>-24.20444205316123</v>
+        <v>-29.73586437015439</v>
       </c>
       <c r="F36">
-        <v>10.77330533754469</v>
+        <v>11.78920833853346</v>
       </c>
       <c r="G36">
-        <v>-2.810101452404513</v>
+        <v>-4.374824180449961</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.011775780734343</v>
       </c>
       <c r="E37">
-        <v>-25.12161653630475</v>
+        <v>-28.85039826201258</v>
       </c>
       <c r="F37">
-        <v>11.28027018925376</v>
+        <v>11.70165949182205</v>
       </c>
       <c r="G37">
-        <v>-3.133783421415675</v>
+        <v>-6.291914754604356</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.868022889154743</v>
       </c>
       <c r="E38">
-        <v>-23.97419179224123</v>
+        <v>-29.46594014845319</v>
       </c>
       <c r="F38">
-        <v>10.76291305932758</v>
+        <v>11.3860189843454</v>
       </c>
       <c r="G38">
-        <v>-2.928774578350767</v>
+        <v>-6.662841519006457</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.691499325278787</v>
       </c>
       <c r="E39">
-        <v>-22.69395596248076</v>
+        <v>-28.40055776798664</v>
       </c>
       <c r="F39">
-        <v>10.61412705598387</v>
+        <v>12.08393600939674</v>
       </c>
       <c r="G39">
-        <v>-4.632798441597669</v>
+        <v>-5.47235941144792</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.483257767376866</v>
       </c>
       <c r="E40">
-        <v>-20.87559703791482</v>
+        <v>-27.78309128009277</v>
       </c>
       <c r="F40">
-        <v>11.05842941573675</v>
+        <v>12.34590947451691</v>
       </c>
       <c r="G40">
-        <v>-3.957284934854922</v>
+        <v>-5.345211288921131</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.240932741168704</v>
       </c>
       <c r="E41">
-        <v>-22.31316111164977</v>
+        <v>-28.3820544231913</v>
       </c>
       <c r="F41">
-        <v>10.93310284811845</v>
+        <v>11.71492302886386</v>
       </c>
       <c r="G41">
-        <v>-2.911622641911804</v>
+        <v>-6.735792700509837</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.967012456917421</v>
       </c>
       <c r="E42">
-        <v>-19.60847114040655</v>
+        <v>-24.53561388581618</v>
       </c>
       <c r="F42">
-        <v>10.47647133781387</v>
+        <v>11.4429389586522</v>
       </c>
       <c r="G42">
-        <v>-3.509583308851583</v>
+        <v>-7.248397571810587</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.670840172844422</v>
       </c>
       <c r="E43">
-        <v>-19.88025203645089</v>
+        <v>-25.77837206468917</v>
       </c>
       <c r="F43">
-        <v>10.91590538558269</v>
+        <v>11.95854767724774</v>
       </c>
       <c r="G43">
-        <v>-4.297860617752985</v>
+        <v>-7.946200981669246</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.356943017379502</v>
       </c>
       <c r="E44">
-        <v>-18.62859540615283</v>
+        <v>-25.83086160691207</v>
       </c>
       <c r="F44">
-        <v>10.73248373386832</v>
+        <v>12.0648935294695</v>
       </c>
       <c r="G44">
-        <v>-4.297546115926754</v>
+        <v>-8.483807092882573</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.029812403484931</v>
       </c>
       <c r="E45">
-        <v>-19.75811003551601</v>
+        <v>-24.01732097869029</v>
       </c>
       <c r="F45">
-        <v>10.77962115673546</v>
+        <v>12.52092006411437</v>
       </c>
       <c r="G45">
-        <v>-4.399378496714736</v>
+        <v>-6.779160847074289</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.691322281585936</v>
       </c>
       <c r="E46">
-        <v>-19.59495817396766</v>
+        <v>-26.27623702556645</v>
       </c>
       <c r="F46">
-        <v>11.28530320665302</v>
+        <v>12.08558147984289</v>
       </c>
       <c r="G46">
-        <v>-3.428478253684978</v>
+        <v>-6.906722787793487</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.350357736029298</v>
       </c>
       <c r="E47">
-        <v>-18.2023799610249</v>
+        <v>-26.00969104547497</v>
       </c>
       <c r="F47">
-        <v>10.66257737105491</v>
+        <v>11.6670555175697</v>
       </c>
       <c r="G47">
-        <v>-3.557420691894052</v>
+        <v>-8.035608885048344</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.018863679630307</v>
       </c>
       <c r="E48">
-        <v>-18.38937876669764</v>
+        <v>-24.35554364537517</v>
       </c>
       <c r="F48">
-        <v>10.93774944127435</v>
+        <v>11.56080627140879</v>
       </c>
       <c r="G48">
-        <v>-3.112758146695764</v>
+        <v>-7.751140327949849</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.703865317327294</v>
       </c>
       <c r="E49">
-        <v>-17.24557227336626</v>
+        <v>-21.53252917678553</v>
       </c>
       <c r="F49">
-        <v>10.79917200626156</v>
+        <v>11.81691368981816</v>
       </c>
       <c r="G49">
-        <v>-2.674514749298122</v>
+        <v>-7.923397943994747</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.411067212649127</v>
       </c>
       <c r="E50">
-        <v>-18.05609666515513</v>
+        <v>-22.85363901293923</v>
       </c>
       <c r="F50">
-        <v>10.70381548938704</v>
+        <v>11.67021184345917</v>
       </c>
       <c r="G50">
-        <v>-3.035791273453248</v>
+        <v>-5.747876253408226</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.142131130709392</v>
       </c>
       <c r="E51">
-        <v>-15.15644230245968</v>
+        <v>-23.44041150400911</v>
       </c>
       <c r="F51">
-        <v>11.14706151729431</v>
+        <v>11.56471010649034</v>
       </c>
       <c r="G51">
-        <v>-3.916247412350117</v>
+        <v>-7.074348950628944</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.904953202865253</v>
       </c>
       <c r="E52">
-        <v>-16.43011637338303</v>
+        <v>-19.72837607518164</v>
       </c>
       <c r="F52">
-        <v>10.98907734999374</v>
+        <v>11.88311259708353</v>
       </c>
       <c r="G52">
-        <v>-4.372129396380995</v>
+        <v>-6.816027082199613</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.704598569506976</v>
       </c>
       <c r="E53">
-        <v>-14.85403533670146</v>
+        <v>-22.21571740795272</v>
       </c>
       <c r="F53">
-        <v>10.76561961273706</v>
+        <v>12.24725409822052</v>
       </c>
       <c r="G53">
-        <v>-4.330807166959811</v>
+        <v>-7.230788780087204</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.541608161161197</v>
       </c>
       <c r="E54">
-        <v>-14.97595091393596</v>
+        <v>-22.84282048853491</v>
       </c>
       <c r="F54">
-        <v>10.93696392314029</v>
+        <v>11.72819448443524</v>
       </c>
       <c r="G54">
-        <v>-2.381491742526151</v>
+        <v>-7.218907232146759</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.413442346218288</v>
       </c>
       <c r="E55">
-        <v>-15.0235044194905</v>
+        <v>-18.76924980883107</v>
       </c>
       <c r="F55">
-        <v>11.11764734732686</v>
+        <v>11.89133044707875</v>
       </c>
       <c r="G55">
-        <v>-2.722620286529272</v>
+        <v>-7.037294014407881</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.314426547966899</v>
       </c>
       <c r="E56">
-        <v>-13.78454110183594</v>
+        <v>-18.73220236297432</v>
       </c>
       <c r="F56">
-        <v>10.48891451519148</v>
+        <v>12.21939037634428</v>
       </c>
       <c r="G56">
-        <v>-3.375559183239729</v>
+        <v>-5.98428562091312</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.245225589506225</v>
       </c>
       <c r="E57">
-        <v>-14.28704774857109</v>
+        <v>-17.77465653405242</v>
       </c>
       <c r="F57">
-        <v>11.02383969483763</v>
+        <v>11.87661306800657</v>
       </c>
       <c r="G57">
-        <v>-3.657131012991361</v>
+        <v>-6.995690388615861</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.202484876330915</v>
       </c>
       <c r="E58">
-        <v>-13.50688224652964</v>
+        <v>-20.07403902466113</v>
       </c>
       <c r="F58">
-        <v>10.8636335881377</v>
+        <v>12.29287591452659</v>
       </c>
       <c r="G58">
-        <v>-2.374781266718049</v>
+        <v>-7.137974325348197</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.180378070341949</v>
       </c>
       <c r="E59">
-        <v>-13.12988678539108</v>
+        <v>-16.68864695448093</v>
       </c>
       <c r="F59">
-        <v>10.84642662336644</v>
+        <v>12.33530339600121</v>
       </c>
       <c r="G59">
-        <v>-2.903478699885197</v>
+        <v>-6.833910649202756</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.17053218178387</v>
       </c>
       <c r="E60">
-        <v>-12.2699974984446</v>
+        <v>-16.87113540004203</v>
       </c>
       <c r="F60">
-        <v>11.02910710071239</v>
+        <v>11.84049190348722</v>
       </c>
       <c r="G60">
-        <v>-2.021158723849718</v>
+        <v>-6.775098807697604</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.163858034542651</v>
       </c>
       <c r="E61">
-        <v>-12.16931140735805</v>
+        <v>-16.06424737288132</v>
       </c>
       <c r="F61">
-        <v>10.74007760373286</v>
+        <v>12.05165216431051</v>
       </c>
       <c r="G61">
-        <v>-3.526212179095342</v>
+        <v>-6.265595917567151</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.15740010706272</v>
       </c>
       <c r="E62">
-        <v>-12.93758060818135</v>
+        <v>-16.56525962319394</v>
       </c>
       <c r="F62">
-        <v>11.1218568376501</v>
+        <v>12.34995425942494</v>
       </c>
       <c r="G62">
-        <v>-4.079106389609024</v>
+        <v>-7.005115511766165</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.145786813834783</v>
       </c>
       <c r="E63">
-        <v>-10.9243886179094</v>
+        <v>-16.69686160633085</v>
       </c>
       <c r="F63">
-        <v>11.10830506613168</v>
+        <v>12.72606065875308</v>
       </c>
       <c r="G63">
-        <v>-3.609859733236108</v>
+        <v>-6.981309378793267</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.125088265978249</v>
       </c>
       <c r="E64">
-        <v>-11.69011734481439</v>
+        <v>-14.82208695257734</v>
       </c>
       <c r="F64">
-        <v>11.1976086589974</v>
+        <v>12.00971879908151</v>
       </c>
       <c r="G64">
-        <v>-3.592800492072243</v>
+        <v>-8.0839594026494</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.091399115832468</v>
       </c>
       <c r="E65">
-        <v>-11.25903379012822</v>
+        <v>-16.59299652649092</v>
       </c>
       <c r="F65">
-        <v>10.92870172937944</v>
+        <v>11.51420572484698</v>
       </c>
       <c r="G65">
-        <v>-3.388798054851274</v>
+        <v>-6.858491449831845</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.044752636150021</v>
       </c>
       <c r="E66">
-        <v>-9.551006606285153</v>
+        <v>-15.00846082883702</v>
       </c>
       <c r="F66">
-        <v>10.68767594240279</v>
+        <v>12.00361836389523</v>
       </c>
       <c r="G66">
-        <v>-3.394038648439941</v>
+        <v>-7.901074935423441</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.989920341658592</v>
       </c>
       <c r="E67">
-        <v>-10.33812331592838</v>
+        <v>-14.65059364190686</v>
       </c>
       <c r="F67">
-        <v>11.07451036560212</v>
+        <v>11.6599779358336</v>
       </c>
       <c r="G67">
-        <v>-3.22792540491593</v>
+        <v>-8.90085306719226</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.929395702618109</v>
       </c>
       <c r="E68">
-        <v>-10.43559419046947</v>
+        <v>-12.15798116539086</v>
       </c>
       <c r="F68">
-        <v>11.20300909616904</v>
+        <v>12.24794617770557</v>
       </c>
       <c r="G68">
-        <v>-3.739172952545579</v>
+        <v>-8.700568372611894</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.86586711448445</v>
       </c>
       <c r="E69">
-        <v>-11.11759596144665</v>
+        <v>-12.82896063063337</v>
       </c>
       <c r="F69">
-        <v>11.00646960835709</v>
+        <v>11.92456134830241</v>
       </c>
       <c r="G69">
-        <v>-3.623039015027946</v>
+        <v>-8.363356203981731</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.799333345925009</v>
       </c>
       <c r="E70">
-        <v>-11.38896929483031</v>
+        <v>-13.33724561020231</v>
       </c>
       <c r="F70">
-        <v>10.6736031316382</v>
+        <v>12.44367797550064</v>
       </c>
       <c r="G70">
-        <v>-3.901257262148297</v>
+        <v>-7.692666162089703</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.733803472390726</v>
       </c>
       <c r="E71">
-        <v>-10.82124356543669</v>
+        <v>-16.1781792504403</v>
       </c>
       <c r="F71">
-        <v>11.00688929042468</v>
+        <v>11.64845014047512</v>
       </c>
       <c r="G71">
-        <v>-3.966312792540515</v>
+        <v>-8.727393723116608</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.673882389049081</v>
       </c>
       <c r="E72">
-        <v>-10.84827402678847</v>
+        <v>-14.92318966327259</v>
       </c>
       <c r="F72">
-        <v>10.99886781996298</v>
+        <v>11.70973480828488</v>
       </c>
       <c r="G72">
-        <v>-4.541318136710988</v>
+        <v>-8.306603521802005</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.621192175658007</v>
       </c>
       <c r="E73">
-        <v>-9.857588825078444</v>
+        <v>-12.93948709573858</v>
       </c>
       <c r="F73">
-        <v>11.16505400019962</v>
+        <v>11.28704686686592</v>
       </c>
       <c r="G73">
-        <v>-4.65909079427056</v>
+        <v>-9.227670122829112</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.575861353193867</v>
       </c>
       <c r="E74">
-        <v>-11.07245160406419</v>
+        <v>-14.30063769906811</v>
       </c>
       <c r="F74">
-        <v>10.08325457977533</v>
+        <v>11.3061542787357</v>
       </c>
       <c r="G74">
-        <v>-4.347091740467487</v>
+        <v>-7.248639241634955</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.534921902114683</v>
       </c>
       <c r="E75">
-        <v>-9.502112672424335</v>
+        <v>-12.40276329940148</v>
       </c>
       <c r="F75">
-        <v>10.65908529951137</v>
+        <v>11.44873848971454</v>
       </c>
       <c r="G75">
-        <v>-4.025197466047532</v>
+        <v>-7.187870867716092</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.499338542790791</v>
       </c>
       <c r="E76">
-        <v>-9.780065878541135</v>
+        <v>-13.17472320654103</v>
       </c>
       <c r="F76">
-        <v>10.50218280335103</v>
+        <v>11.36321203545715</v>
       </c>
       <c r="G76">
-        <v>-3.854737476230458</v>
+        <v>-8.896704953631554</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.468914628039356</v>
       </c>
       <c r="E77">
-        <v>-10.97989865229542</v>
+        <v>-15.44302225156109</v>
       </c>
       <c r="F77">
-        <v>10.38352838875448</v>
+        <v>10.97656765696768</v>
       </c>
       <c r="G77">
-        <v>-4.927192014222898</v>
+        <v>-7.3294695215218</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.441971344500236</v>
       </c>
       <c r="E78">
-        <v>-11.9644749425691</v>
+        <v>-14.54244009718167</v>
       </c>
       <c r="F78">
-        <v>9.69330025592259</v>
+        <v>10.79352609467302</v>
       </c>
       <c r="G78">
-        <v>-3.452400255751752</v>
+        <v>-6.926304664658276</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.415935281828401</v>
       </c>
       <c r="E79">
-        <v>-11.37188336239937</v>
+        <v>-14.52273217830029</v>
       </c>
       <c r="F79">
-        <v>9.834661845934715</v>
+        <v>11.2574616566596</v>
       </c>
       <c r="G79">
-        <v>-3.429487970074456</v>
+        <v>-6.838422922772783</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.388241889018987</v>
       </c>
       <c r="E80">
-        <v>-12.36121907885511</v>
+        <v>-17.48074045705858</v>
       </c>
       <c r="F80">
-        <v>10.47922540240082</v>
+        <v>11.04469076692031</v>
       </c>
       <c r="G80">
-        <v>-4.258425399289187</v>
+        <v>-6.520752904460938</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.362627198775153</v>
       </c>
       <c r="E81">
-        <v>-11.3861299416275</v>
+        <v>-15.87267933693484</v>
       </c>
       <c r="F81">
-        <v>9.972010325157116</v>
+        <v>11.28131860256978</v>
       </c>
       <c r="G81">
-        <v>-3.228501439839763</v>
+        <v>-7.29935017820551</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.342921319664315</v>
       </c>
       <c r="E82">
-        <v>-14.66913774296827</v>
+        <v>-14.68216616268834</v>
       </c>
       <c r="F82">
-        <v>9.526475842202029</v>
+        <v>10.20576215086415</v>
       </c>
       <c r="G82">
-        <v>-2.594071803239372</v>
+        <v>-6.435582499372107</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.333440256147572</v>
       </c>
       <c r="E83">
-        <v>-12.80708357270232</v>
+        <v>-14.09652126164637</v>
       </c>
       <c r="F83">
-        <v>9.971288155259677</v>
+        <v>9.974507829385765</v>
       </c>
       <c r="G83">
-        <v>-3.833801586240107</v>
+        <v>-7.352504297384049</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.337718352076861</v>
       </c>
       <c r="E84">
-        <v>-14.61113704787803</v>
+        <v>-14.81322472894433</v>
       </c>
       <c r="F84">
-        <v>9.913259586812059</v>
+        <v>10.0757018862646</v>
       </c>
       <c r="G84">
-        <v>-2.936892036013061</v>
+        <v>-5.994091456800442</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.359799657037504</v>
       </c>
       <c r="E85">
-        <v>-15.22537926227844</v>
+        <v>-19.30555245708547</v>
       </c>
       <c r="F85">
-        <v>9.545958592373765</v>
+        <v>10.1666557006942</v>
       </c>
       <c r="G85">
-        <v>-2.92808267433306</v>
+        <v>-6.495741732911744</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.408518249119946</v>
       </c>
       <c r="E86">
-        <v>-15.5749231139825</v>
+        <v>-16.85932966830404</v>
       </c>
       <c r="F86">
-        <v>9.579594922311784</v>
+        <v>10.30963900556374</v>
       </c>
       <c r="G86">
-        <v>-1.714108935627855</v>
+        <v>-7.182901738861646</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.489789033951767</v>
       </c>
       <c r="E87">
-        <v>-16.9499942464116</v>
+        <v>-19.01386891777741</v>
       </c>
       <c r="F87">
-        <v>8.977840520445918</v>
+        <v>9.827886752028464</v>
       </c>
       <c r="G87">
-        <v>-2.118568215797234</v>
+        <v>-5.582557540813641</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.607818429319154</v>
       </c>
       <c r="E88">
-        <v>-17.42843205379598</v>
+        <v>-20.90995457021101</v>
       </c>
       <c r="F88">
-        <v>9.144596834812114</v>
+        <v>9.25807728218293</v>
       </c>
       <c r="G88">
-        <v>-1.148432708787048</v>
+        <v>-4.832043624878705</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.761673208553118</v>
       </c>
       <c r="E89">
-        <v>-21.17788626334884</v>
+        <v>-21.93961634770506</v>
       </c>
       <c r="F89">
-        <v>9.28846226387655</v>
+        <v>9.811568246275776</v>
       </c>
       <c r="G89">
-        <v>-1.546770790254314</v>
+        <v>-3.674839121080923</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.952016695289088</v>
       </c>
       <c r="E90">
-        <v>-21.49653686537257</v>
+        <v>-23.99024523259843</v>
       </c>
       <c r="F90">
-        <v>8.763810584503855</v>
+        <v>9.423351247812274</v>
       </c>
       <c r="G90">
-        <v>-1.07710700514345</v>
+        <v>-2.93012859147633</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.181341898132378</v>
       </c>
       <c r="E91">
-        <v>-22.17763747002222</v>
+        <v>-24.81888804889198</v>
       </c>
       <c r="F91">
-        <v>8.516369204863764</v>
+        <v>9.42288722197905</v>
       </c>
       <c r="G91">
-        <v>-0.09849650155273026</v>
+        <v>-3.718604533110088</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.447526558263172</v>
       </c>
       <c r="E92">
-        <v>-22.257800516906</v>
+        <v>-26.59227922656177</v>
       </c>
       <c r="F92">
-        <v>7.610810913533235</v>
+        <v>8.846489535525286</v>
       </c>
       <c r="G92">
-        <v>-1.558771517834172</v>
+        <v>-3.8825261954871</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.74694983448984</v>
       </c>
       <c r="E93">
-        <v>-24.99751370612454</v>
+        <v>-26.00888950557562</v>
       </c>
       <c r="F93">
-        <v>7.644936608599123</v>
+        <v>8.912659936084177</v>
       </c>
       <c r="G93">
-        <v>-2.057088074587428</v>
+        <v>-2.336544465739467</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.069155688733893</v>
       </c>
       <c r="E94">
-        <v>-26.99633231989615</v>
+        <v>-29.07231613075847</v>
       </c>
       <c r="F94">
-        <v>8.015355919984918</v>
+        <v>7.828435861903346</v>
       </c>
       <c r="G94">
-        <v>-0.06474880032539979</v>
+        <v>-3.671406085356698</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.411216187435417</v>
       </c>
       <c r="E95">
-        <v>-28.80622752654176</v>
+        <v>-29.47151243571963</v>
       </c>
       <c r="F95">
-        <v>7.200553479844561</v>
+        <v>7.534268822934131</v>
       </c>
       <c r="G95">
-        <v>-0.9957006903327718</v>
+        <v>-4.143857349811628</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.773063181515548</v>
       </c>
       <c r="E96">
-        <v>-31.48608561056393</v>
+        <v>-32.98098016523599</v>
       </c>
       <c r="F96">
-        <v>6.67197262609566</v>
+        <v>6.49354598283859</v>
       </c>
       <c r="G96">
-        <v>0.3436732028544865</v>
+        <v>-1.792413269268236</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.146337470104617</v>
       </c>
       <c r="E97">
-        <v>-31.88974699089665</v>
+        <v>-34.34699434964975</v>
       </c>
       <c r="F97">
-        <v>6.054007410479357</v>
+        <v>5.723421470278696</v>
       </c>
       <c r="G97">
-        <v>0.05070316481114358</v>
+        <v>-1.344774543630143</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.534048595385906</v>
       </c>
       <c r="E98">
-        <v>-35.1662405823774</v>
+        <v>-34.06755580405844</v>
       </c>
       <c r="F98">
-        <v>6.095399148285282</v>
+        <v>6.512065839813739</v>
       </c>
       <c r="G98">
-        <v>0.7296166018227216</v>
+        <v>-1.722785875486285</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.916000192077363</v>
       </c>
       <c r="E99">
-        <v>-37.77759870432253</v>
+        <v>-37.84504806042978</v>
       </c>
       <c r="F99">
-        <v>5.759900552334928</v>
+        <v>6.108857481154687</v>
       </c>
       <c r="G99">
-        <v>1.355395782928997</v>
+        <v>-1.062514120406343</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.311833741888321</v>
       </c>
       <c r="E100">
-        <v>-40.10768198446624</v>
+        <v>-38.86993682631974</v>
       </c>
       <c r="F100">
-        <v>4.964713893663204</v>
+        <v>4.857633201896681</v>
       </c>
       <c r="G100">
-        <v>0.7272959093996925</v>
+        <v>-2.232470845621398</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.691102131616611</v>
       </c>
       <c r="E101">
-        <v>-41.33307346551982</v>
+        <v>-41.65962625468693</v>
       </c>
       <c r="F101">
-        <v>4.540603784332182</v>
+        <v>4.736926304433718</v>
       </c>
       <c r="G101">
-        <v>0.4058684219007743</v>
+        <v>-1.479248903435339</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.103568422796055</v>
       </c>
       <c r="E102">
-        <v>-42.70416859777018</v>
+        <v>-45.51243382651684</v>
       </c>
       <c r="F102">
-        <v>4.865296754821493</v>
+        <v>4.322879062489398</v>
       </c>
       <c r="G102">
-        <v>0.6785779212437777</v>
+        <v>-2.586659491776944</v>
       </c>
     </row>
   </sheetData>
